--- a/data/trans_bre/BARTHEL_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/BARTHEL_R2-Clase-trans_bre.xlsx
@@ -612,42 +612,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-1,91</t>
+          <t>1,91</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,38</t>
+          <t>2,38</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,96</t>
+          <t>1,96</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-2,02%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,23%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>-2,49%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-2,07%</t>
+          <t>34,98%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 7,63</t>
+          <t>-7,45; 17,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,53; 13,99</t>
+          <t>-14,55; 17,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 6,24</t>
+          <t>-6,29; 16,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 3,33</t>
+          <t>-3,63; 8,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 8,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 16,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 6,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 3,61</t>
+          <t>-48,73; 262,66</t>
         </is>
       </c>
     </row>
@@ -712,42 +712,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-18,96</t>
+          <t>18,96</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-8,42</t>
+          <t>8,42</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-13,41</t>
+          <t>13,41</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,47</t>
+          <t>5,47</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-19,27%</t>
+          <t>1177,27%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-9,27%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>-15,52%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-5,89%</t>
+          <t>75,84%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,63; -2,31</t>
+          <t>2,71; 44,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,68; 8,7</t>
+          <t>-8,57; 30,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,0; 7,98</t>
+          <t>-9,8; 46,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 1,95</t>
+          <t>-2,81; 13,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,59; -1,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-35,32; 9,7</t>
+          <t>-100,0; 865,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,5; 9,38</t>
+          <t>-86,35; 559,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,9; 2,03</t>
+          <t>-30,58; 293,97</t>
         </is>
       </c>
     </row>
@@ -812,42 +812,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-9,9</t>
+          <t>9,9</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-12,51</t>
+          <t>12,51</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-6,38</t>
+          <t>6,38</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-6,85</t>
+          <t>6,85</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-10,82%</t>
+          <t>116,14%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-13,7%</t>
+          <t>143,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>-7,04%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-7,89%</t>
+          <t>51,86%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-32,09; 4,77</t>
+          <t>-5,44; 32,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-25,65; -1,12</t>
+          <t>0,34; 27,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,44; 3,84</t>
+          <t>-4,43; 20,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 1,6</t>
+          <t>-2,19; 16,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-34,33; 5,1</t>
+          <t>-64,32; 596,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,83; -1,4</t>
+          <t>-6,04; 507,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 4,15</t>
+          <t>-42,91; 354,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 1,73</t>
+          <t>-14,13; 179,27</t>
         </is>
       </c>
     </row>
@@ -912,42 +912,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-2,34</t>
+          <t>2,34</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-10,66</t>
+          <t>10,66</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,64</t>
+          <t>-11,64</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>-0,44%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-2,96%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>-11,88%</t>
+          <t>103,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>-65,11%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 5,79</t>
+          <t>-5,92; 7,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 9,18</t>
+          <t>-8,81; 15,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,71; -1,62</t>
+          <t>1,62; 21,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 22,47</t>
+          <t>-21,86; -0,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 6,54</t>
+          <t>-61,65; 127,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,69; 11,97</t>
+          <t>-38,01; 89,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,1; -1,94</t>
+          <t>8,18; 266,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 30,02</t>
+          <t>-93,5; 0,34</t>
         </is>
       </c>
     </row>
@@ -1012,42 +1012,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-5,93</t>
+          <t>5,93</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-18,5</t>
+          <t>18,5</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,69</t>
+          <t>3,69</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-14,32</t>
+          <t>14,32</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-6,84%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-21,9%</t>
+          <t>119,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>-4,55%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-16,7%</t>
+          <t>100,37%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 8,12</t>
+          <t>-5,83; 18,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-28,02; -7,92</t>
+          <t>7,53; 27,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 5,51</t>
+          <t>-4,93; 14,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,43; -6,93</t>
+          <t>7,44; 21,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 9,8</t>
+          <t>-31,47; 275,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,72; -10,16</t>
+          <t>32,8; 283,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 7,27</t>
+          <t>-23,02; 105,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-23,06; -8,96</t>
+          <t>34,03; 218,91</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-13,03</t>
+          <t>13,03</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-24,41</t>
+          <t>24,41</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1127,17 +1127,17 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,64</t>
+          <t>-7,64</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-13,03%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-24,41%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>-22,41%</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,56; -9,85</t>
+          <t>9,9; 16,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-29,45; -20,31</t>
+          <t>20,03; 29,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,45; 44,24</t>
+          <t>-57,34; 26,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,56; -9,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,45; -20,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,45; 142,06</t>
+          <t>-68,21; —</t>
         </is>
       </c>
     </row>
@@ -1212,42 +1212,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-5,5</t>
+          <t>5,5</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-10,88</t>
+          <t>10,88</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-9,99</t>
+          <t>9,99</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-5,17</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-5,98%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-12,79%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>-11,34%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-5,94%</t>
+          <t>39,69%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,05; -1,95</t>
+          <t>2,04; 9,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,7; -5,96</t>
+          <t>6,37; 15,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,6; -5,89</t>
+          <t>6,39; 14,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 3,42</t>
+          <t>-4,98; 10,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,71; -2,26</t>
+          <t>21,29; 145,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,93; -7,3</t>
+          <t>36,11; 122,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,23; -6,74</t>
+          <t>45,92; 150,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 3,97</t>
+          <t>-30,49; 89,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/BARTHEL_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/BARTHEL_R2-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dependencia funcional, al menos moderada, para actividades básicas de la vida diaria (Barthel)</t>
+          <t>Población con dependencia funcional para actividades básicas de la vida diaria de grado moderado o superior (Barthel)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,96</t>
+          <t>2,18</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 17,17</t>
+          <t>-7,14; 16,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 17,28</t>
+          <t>-14,05; 17,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 16,35</t>
+          <t>-5,81; 17,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 8,31</t>
+          <t>-2,7; 8,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-48,73; 262,66</t>
+          <t>-44,75; 265,62</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,44</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>79,2%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 44,21</t>
+          <t>2,33; 46,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 30,86</t>
+          <t>-7,72; 35,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 46,7</t>
+          <t>-7,78; 45,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 13,8</t>
+          <t>-2,14; 13,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,17 +785,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 865,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-86,35; 559,27</t>
+          <t>-60,26; 646,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,58; 293,97</t>
+          <t>-31,05; 345,53</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,85</t>
+          <t>8,08</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>63,74%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 32,55</t>
+          <t>-3,02; 31,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 27,42</t>
+          <t>1,54; 27,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 20,41</t>
+          <t>-4,02; 20,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 16,77</t>
+          <t>-0,57; 18,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-64,32; 596,08</t>
+          <t>-45,78; 692,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 507,35</t>
+          <t>-3,83; 482,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-42,91; 354,1</t>
+          <t>-41,64; 330,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 179,27</t>
+          <t>-5,27; 198,9</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-11,64</t>
+          <t>-0,42</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-65,11%</t>
+          <t>-2,4%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 7,87</t>
+          <t>-6,05; 8,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 15,23</t>
+          <t>-9,68; 15,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 21,98</t>
+          <t>1,85; 21,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,86; -0,37</t>
+          <t>-6,41; 5,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,65; 127,17</t>
+          <t>-58,91; 119,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 89,95</t>
+          <t>-43,2; 86,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,18; 266,04</t>
+          <t>11,43; 266,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-93,5; 0,34</t>
+          <t>-30,39; 38,33</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,32</t>
+          <t>15,69</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>100,37%</t>
+          <t>118,21%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 18,24</t>
+          <t>-7,53; 17,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,53; 27,87</t>
+          <t>7,84; 27,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 14,24</t>
+          <t>-5,9; 12,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,44; 21,59</t>
+          <t>8,74; 22,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-31,47; 275,83</t>
+          <t>-38,52; 257,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,8; 283,78</t>
+          <t>31,15; 262,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 105,64</t>
+          <t>-26,17; 89,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>34,03; 218,91</t>
+          <t>45,56; 232,68</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-7,64</t>
+          <t>-9,18</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-22,41%</t>
+          <t>-25,48%</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,9; 16,45</t>
+          <t>9,8; 16,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,03; 29,07</t>
+          <t>20,44; 29,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-57,34; 26,3</t>
+          <t>-57,4; 27,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,21; —</t>
+          <t>-67,98; —</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,17</t>
+          <t>10,47</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>83,76%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 9,0</t>
+          <t>2,26; 9,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,37; 15,11</t>
+          <t>6,48; 15,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,39; 14,84</t>
+          <t>5,8; 14,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 10,97</t>
+          <t>7,28; 12,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,29; 145,89</t>
+          <t>23,03; 147,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,11; 122,5</t>
+          <t>37,06; 125,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,92; 150,74</t>
+          <t>42,65; 137,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-30,49; 89,88</t>
+          <t>50,84; 118,16</t>
         </is>
       </c>
     </row>
